--- a/data/trans_orig/IP07KS_C02_2023-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP07KS_C02_2023-Edad-trans_orig.xlsx
@@ -535,13 +535,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según la frecuencia de sentirse lleno/a de energía en 2023 (tasa de respuesta: 99,83%)</t>
+          <t>Menores según la frecuencia de sentirse lleno/a de energía, percibida por el/la menor [KIDSCREEN 10] en 2023 (tasa de respuesta: 99,83%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -720,72 +720,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>65557</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>57351</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>73976</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>66,54%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>58,21%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>75,09%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>58</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>42823</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>35961</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>49219</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>63,04%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>52,94%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>72,46%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>76</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>66115</t>
+          <t>44938</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>56717</t>
+          <t>37788</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>74233</t>
+          <t>51873</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>66,54%</t>
+          <t>62,76%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>57,08%</t>
+          <t>52,77%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>74,71%</t>
+          <t>72,44%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>108938</t>
+          <t>110495</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>97652</t>
+          <t>99575</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>119215</t>
+          <t>121255</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>65,12%</t>
+          <t>64,95%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>58,37%</t>
+          <t>58,53%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>71,26%</t>
+          <t>71,27%</t>
         </is>
       </c>
     </row>
@@ -833,72 +833,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>22487</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>15162</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>30470</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>22,83%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>15,39%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>30,93%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>31</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>21078</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>15077</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>27383</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>31,03%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>22,2%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>40,31%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>22441</t>
+          <t>21974</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>15930</t>
+          <t>16214</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>31026</t>
+          <t>29226</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>22,58%</t>
+          <t>30,69%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>16,03%</t>
+          <t>22,64%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>31,22%</t>
+          <t>40,82%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>43519</t>
+          <t>44461</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>34692</t>
+          <t>34734</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>53354</t>
+          <t>54785</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>26,01%</t>
+          <t>26,13%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>20,74%</t>
+          <t>20,42%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>31,89%</t>
+          <t>32,2%</t>
         </is>
       </c>
     </row>
@@ -946,72 +946,72 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>6369</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>3259</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>11894</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>6,47%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>3,31%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>12,07%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>3861</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>1291</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>8531</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>5,68%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>1,9%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>12,56%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>6543</t>
+          <t>4313</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>3217</t>
+          <t>1642</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>11781</t>
+          <t>9927</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>6,58%</t>
+          <t>6,02%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>11,86%</t>
+          <t>13,86%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>10404</t>
+          <t>10682</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>5992</t>
+          <t>6246</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>17775</t>
+          <t>17091</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>6,28%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>10,62%</t>
+          <t>10,05%</t>
         </is>
       </c>
     </row>
@@ -1064,7 +1064,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>163</t>
+          <t>999</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -1074,12 +1074,12 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>843</t>
+          <t>5584</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>5,67%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1080</t>
+          <t>382</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>5436</t>
+          <t>1943</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1134,7 +1134,7 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>1243</t>
+          <t>1381</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
@@ -1144,12 +1144,12 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>6498</t>
+          <t>5909</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
@@ -1159,7 +1159,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>3,47%</t>
         </is>
       </c>
     </row>
@@ -1172,107 +1172,107 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>3107</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>921</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>7557</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>3,15%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>0,93%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>7,67%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="M8" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
+      <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>3186</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>934</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>8716</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>3,21%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>0,94%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>8,77%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>3186</t>
+          <t>3107</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>976</t>
+          <t>904</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>7995</t>
+          <t>7793</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>4,58%</t>
         </is>
       </c>
     </row>
@@ -1285,74 +1285,74 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>119</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>98519</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>98519</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>98519</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>95</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>67925</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>67925</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>67925</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>71606</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>71606</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>71606</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
+      <c r="O9" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="I9" s="2" t="inlineStr">
+      <c r="P9" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>119</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>99365</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>99365</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>99365</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="O9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="P9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
       <c r="Q9" s="2" t="inlineStr">
         <is>
           <t>214</t>
@@ -1360,17 +1360,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>167290</t>
+          <t>170125</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>167290</t>
+          <t>170125</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>167290</t>
+          <t>170125</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1402,72 +1402,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>108</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>98154</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>84434</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>113262</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>57,54%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>49,5%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>66,39%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>101</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>93751</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>78963</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>115292</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>65,77%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>55,39%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>80,88%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>108</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>100257</t>
+          <t>74442</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>85348</t>
+          <t>63509</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>117085</t>
+          <t>83071</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>58,44%</t>
+          <t>59,09%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>49,75%</t>
+          <t>50,41%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>68,25%</t>
+          <t>65,94%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>194008</t>
+          <t>172596</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>172843</t>
+          <t>155411</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>225422</t>
+          <t>190851</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>61,77%</t>
+          <t>58,2%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>55,03%</t>
+          <t>52,4%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>71,77%</t>
+          <t>64,35%</t>
         </is>
       </c>
     </row>
@@ -1515,72 +1515,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>62167</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>47921</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>75686</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>36,44%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>28,09%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>44,37%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>61</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>41003</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>22464</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>54368</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>28,76%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>15,76%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>38,14%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>71</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>60243</t>
+          <t>42995</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>45044</t>
+          <t>34423</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>75374</t>
+          <t>52651</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>35,12%</t>
+          <t>34,13%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>26,26%</t>
+          <t>27,32%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>43,94%</t>
+          <t>41,79%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1590,32 +1590,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>101246</t>
+          <t>105162</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>72852</t>
+          <t>87736</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>120319</t>
+          <t>123602</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>32,23%</t>
+          <t>35,46%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>23,19%</t>
+          <t>29,58%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>38,31%</t>
+          <t>41,68%</t>
         </is>
       </c>
     </row>
@@ -1628,72 +1628,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>8237</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>2546</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>24922</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>4,83%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>1,49%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>14,61%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>6523</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>2558</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>12056</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>4,58%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>1,79%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>8,46%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>9096</t>
+          <t>7203</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>2916</t>
+          <t>3883</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>25829</t>
+          <t>13009</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>5,72%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>15,06%</t>
+          <t>10,33%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1703,32 +1703,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>15619</t>
+          <t>15440</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>7941</t>
+          <t>8359</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>34523</t>
+          <t>29829</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>5,21%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>10,99%</t>
+          <t>10,06%</t>
         </is>
       </c>
     </row>
@@ -1741,107 +1741,107 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>2033</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>7148</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>1,19%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>4,19%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="M13" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
+      <c r="P13" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J13" s="2" t="inlineStr">
+      <c r="Q13" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>1951</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>2033</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>7217</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>1,14%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>7522</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>0,69%</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>4,21%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>1951</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>6804</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>0,62%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,54%</t>
         </is>
       </c>
     </row>
@@ -1854,107 +1854,107 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>1269</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>1343</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>4471</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>0,89%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>4752</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>1,07%</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>3,14%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>3,77%</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>1343</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>4801</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>0,45%</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>1269</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>4678</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>0,4%</t>
-        </is>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,62%</t>
         </is>
       </c>
     </row>
@@ -1967,74 +1967,74 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>187</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>170591</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>170591</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>170591</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>175</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>142547</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>142547</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>142547</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>125982</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>125982</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>125982</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="H15" s="2" t="inlineStr">
+      <c r="O15" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="I15" s="2" t="inlineStr">
+      <c r="P15" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>187</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>171547</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>171547</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>171547</t>
-        </is>
-      </c>
-      <c r="N15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="O15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="P15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
       <c r="Q15" s="2" t="inlineStr">
         <is>
           <t>362</t>
@@ -2042,17 +2042,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>314094</t>
+          <t>296573</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>314094</t>
+          <t>296573</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>314094</t>
+          <t>296573</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2084,72 +2084,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>184</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>163711</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>146448</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>181516</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>60,83%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>54,42%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>67,45%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>159</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>136574</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>119750</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>165248</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>64,89%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>56,9%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>78,51%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>184</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>166372</t>
+          <t>119379</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>148053</t>
+          <t>106870</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>185299</t>
+          <t>131838</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>61,41%</t>
+          <t>60,42%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>54,65%</t>
+          <t>54,09%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>68,4%</t>
+          <t>66,72%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2159,32 +2159,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>302946</t>
+          <t>283091</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>281090</t>
+          <t>261038</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>336945</t>
+          <t>302017</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>62,93%</t>
+          <t>60,66%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>58,39%</t>
+          <t>55,93%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>70,0%</t>
+          <t>64,71%</t>
         </is>
       </c>
     </row>
@@ -2197,72 +2197,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>84654</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>68859</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>101604</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>31,46%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>25,59%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>37,76%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>92</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>62081</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>37962</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>76506</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>29,5%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>18,04%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>36,35%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>82684</t>
+          <t>64968</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>64712</t>
+          <t>53831</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>99353</t>
+          <t>77034</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>30,52%</t>
+          <t>32,88%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>23,89%</t>
+          <t>27,24%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>36,67%</t>
+          <t>38,99%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2272,32 +2272,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>144765</t>
+          <t>149622</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>117545</t>
+          <t>130502</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>166090</t>
+          <t>168680</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>30,07%</t>
+          <t>32,06%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>24,42%</t>
+          <t>27,96%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>34,5%</t>
+          <t>36,14%</t>
         </is>
       </c>
     </row>
@@ -2310,72 +2310,72 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>14606</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>7833</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>28714</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>5,43%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>2,91%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>10,67%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>16</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>10384</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>5591</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>17239</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>4,93%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>2,66%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>8,19%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>15639</t>
+          <t>11516</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>9006</t>
+          <t>6628</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>37399</t>
+          <t>18743</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>5,83%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>13,8%</t>
+          <t>9,49%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2385,32 +2385,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>26023</t>
+          <t>26122</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>16754</t>
+          <t>17546</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>42008</t>
+          <t>42332</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>8,73%</t>
+          <t>9,07%</t>
         </is>
       </c>
     </row>
@@ -2423,72 +2423,72 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>3032</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>849</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>8211</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>1,13%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>0,32%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>3,05%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>163</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>382</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>867</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>0,08%</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>2123</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>0,19%</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>0,41%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>3031</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>730</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>8450</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>1,12%</t>
-        </is>
-      </c>
-      <c r="O19" s="2" t="inlineStr">
-        <is>
-          <t>0,27%</t>
-        </is>
-      </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2498,32 +2498,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>3194</t>
+          <t>3414</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>973</t>
+          <t>982</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>8984</t>
+          <t>9318</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>2,0%</t>
         </is>
       </c>
     </row>
@@ -2536,107 +2536,107 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>3107</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>940</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>7775</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>1,15%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>0,35%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>2,89%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>1269</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>1343</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>4664</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>0,6%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>4759</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>0,68%</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>2,22%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>3186</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>885</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>8008</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>1,18%</t>
-        </is>
-      </c>
-      <c r="O20" s="2" t="inlineStr">
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>2,41%</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="R20" s="2" t="inlineStr">
+        <is>
+          <t>4449</t>
+        </is>
+      </c>
+      <c r="S20" s="2" t="inlineStr">
+        <is>
+          <t>1563</t>
+        </is>
+      </c>
+      <c r="T20" s="2" t="inlineStr">
+        <is>
+          <t>10053</t>
+        </is>
+      </c>
+      <c r="U20" s="2" t="inlineStr">
+        <is>
+          <t>0,95%</t>
+        </is>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
         <is>
           <t>0,33%</t>
         </is>
       </c>
-      <c r="P20" s="2" t="inlineStr">
-        <is>
-          <t>2,96%</t>
-        </is>
-      </c>
-      <c r="Q20" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="R20" s="2" t="inlineStr">
-        <is>
-          <t>4456</t>
-        </is>
-      </c>
-      <c r="S20" s="2" t="inlineStr">
-        <is>
-          <t>1736</t>
-        </is>
-      </c>
-      <c r="T20" s="2" t="inlineStr">
-        <is>
-          <t>10465</t>
-        </is>
-      </c>
-      <c r="U20" s="2" t="inlineStr">
-        <is>
-          <t>0,93%</t>
-        </is>
-      </c>
-      <c r="V20" s="2" t="inlineStr">
-        <is>
-          <t>0,36%</t>
-        </is>
-      </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,15%</t>
         </is>
       </c>
     </row>
@@ -2649,74 +2649,74 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>306</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>269110</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>269110</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>269110</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>270</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>210472</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>210472</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>210472</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>197588</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>197588</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>197588</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="H21" s="2" t="inlineStr">
+      <c r="O21" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="I21" s="2" t="inlineStr">
+      <c r="P21" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>306</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>270912</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>270912</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>270912</t>
-        </is>
-      </c>
-      <c r="N21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="O21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="P21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
       <c r="Q21" s="2" t="inlineStr">
         <is>
           <t>576</t>
@@ -2724,17 +2724,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>481384</t>
+          <t>466698</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>481384</t>
+          <t>466698</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>481384</t>
+          <t>466698</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
